--- a/Haplotypes_identification_key.xlsx
+++ b/Haplotypes_identification_key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\FSHD\DUCKS4_2.1_GITHUB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\GITHUB\v1.1\ducks4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55455FAE-C00F-4A70-8013-ABCFDAC30A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3542E58F-795D-4154-8FAE-5325DC832277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HP-identifiction-KEY" sheetId="16" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="HP_regions" sheetId="13" r:id="rId4"/>
     <sheet name="AS_regions" sheetId="14" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="222">
   <si>
     <t>FSHD - rare Haplotypes and how to distinguish them!</t>
   </si>
@@ -622,9 +625,6 @@
     <t>Haplotype results</t>
   </si>
   <si>
-    <t>manual check (in most cases not necessary)</t>
-  </si>
-  <si>
     <t>Sub-haplotype</t>
   </si>
   <si>
@@ -746,6 +746,12 @@
   </si>
   <si>
     <t>The 4qB-pLAM sequence differs so strongly from 4qA/10qA pLAM that it even doesn't cause a blast hit for 4qA/10qA pLAM.</t>
+  </si>
+  <si>
+    <t>manual check</t>
+  </si>
+  <si>
+    <t>c4/c10-mix</t>
   </si>
 </sst>
 </file>
@@ -2240,6 +2246,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2254,14 +2268,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2835,7 +2841,7 @@
     <row r="19" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:14" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="159" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C20" s="160"/>
       <c r="D20" s="160"/>
@@ -2866,7 +2872,7 @@
       <c r="J21" s="184"/>
       <c r="K21" s="174"/>
       <c r="L21" s="186" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="M21" s="174"/>
       <c r="N21" s="187" t="s">
@@ -2900,10 +2906,10 @@
         <v>11</v>
       </c>
       <c r="K22" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="L22" s="42" t="s">
         <v>187</v>
-      </c>
-      <c r="L22" s="42" t="s">
-        <v>188</v>
       </c>
       <c r="M22" s="43" t="s">
         <v>14</v>
@@ -2924,13 +2930,13 @@
         <v>19</v>
       </c>
       <c r="F23" s="162" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="H23" s="44" t="s">
         <v>190</v>
-      </c>
-      <c r="H23" s="44" t="s">
-        <v>191</v>
       </c>
       <c r="I23" s="45" t="s">
         <v>20</v>
@@ -2945,7 +2951,7 @@
         <v>21</v>
       </c>
       <c r="M23" s="48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N23" s="49" t="s">
         <v>22</v>
@@ -2970,11 +2976,11 @@
         <v>28</v>
       </c>
       <c r="K24" s="54" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L24" s="162"/>
       <c r="M24" s="55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N24" s="45" t="s">
         <v>24</v>
@@ -2989,10 +2995,10 @@
         <v>36</v>
       </c>
       <c r="G25" s="180" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" s="180" t="s">
         <v>190</v>
-      </c>
-      <c r="H25" s="180" t="s">
-        <v>191</v>
       </c>
       <c r="I25" s="178" t="s">
         <v>20</v>
@@ -3001,11 +3007,11 @@
         <v>62</v>
       </c>
       <c r="K25" s="56" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L25" s="176"/>
       <c r="M25" s="57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N25" s="45" t="s">
         <v>24</v>
@@ -3093,10 +3099,10 @@
         <v>36</v>
       </c>
       <c r="G29" s="168" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H29" s="172" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I29" s="162" t="s">
         <v>20</v>
@@ -3105,7 +3111,7 @@
         <v>63</v>
       </c>
       <c r="K29" s="60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L29" s="45" t="s">
         <v>37</v>
@@ -3126,7 +3132,7 @@
       <c r="I30" s="166"/>
       <c r="J30" s="166"/>
       <c r="K30" s="60" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L30" s="45" t="s">
         <v>29</v>
@@ -3191,10 +3197,10 @@
         <v>36</v>
       </c>
       <c r="G33" s="65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H33" s="65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I33" s="59" t="s">
         <v>20</v>
@@ -3230,10 +3236,10 @@
         <v>36</v>
       </c>
       <c r="G34" s="168" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H34" s="168" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I34" s="162" t="s">
         <v>20</v>
@@ -3309,10 +3315,10 @@
         <v>36</v>
       </c>
       <c r="G37" s="65" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H37" s="65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I37" s="59" t="s">
         <v>20</v>
@@ -3353,16 +3359,16 @@
         <v>55</v>
       </c>
       <c r="L38" s="70" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M38" s="57"/>
       <c r="N38" s="70" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H39" s="72"/>
       <c r="I39" s="72"/>
@@ -3376,7 +3382,7 @@
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M40" s="73" t="s">
         <v>3</v>
@@ -3384,20 +3390,20 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="M41" s="75" t="s">
         <v>203</v>
-      </c>
-      <c r="M41" s="75" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="M42" s="73" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="M43" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3476,7 +3482,7 @@
   <sheetData>
     <row r="1" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B1" s="77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V1" s="79"/>
       <c r="Z1" s="79"/>
@@ -3511,71 +3517,71 @@
         <v>72</v>
       </c>
       <c r="J3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K3" t="s">
         <v>73</v>
       </c>
       <c r="L3" t="s">
+        <v>210</v>
+      </c>
+      <c r="M3" t="s">
         <v>211</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>212</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>213</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>214</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>215</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>216</v>
-      </c>
-      <c r="R3" t="s">
-        <v>217</v>
       </c>
       <c r="V3" s="79"/>
       <c r="Z3" s="79"/>
       <c r="AA3" s="79"/>
     </row>
     <row r="4" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B4" s="210" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
-      <c r="F4" s="211"/>
-      <c r="G4" s="211"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="211"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="211"/>
-      <c r="L4" s="211"/>
-      <c r="M4" s="211"/>
-      <c r="N4" s="211"/>
-      <c r="O4" s="211"/>
-      <c r="P4" s="211"/>
-      <c r="Q4" s="211"/>
-      <c r="R4" s="212"/>
-      <c r="S4" s="213" t="s">
+      <c r="B4" s="214" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="215"/>
+      <c r="D4" s="215"/>
+      <c r="E4" s="215"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="215"/>
+      <c r="H4" s="215"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="215"/>
+      <c r="L4" s="215"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="215"/>
+      <c r="P4" s="215"/>
+      <c r="Q4" s="215"/>
+      <c r="R4" s="216"/>
+      <c r="S4" s="217" t="s">
         <v>13</v>
       </c>
-      <c r="T4" s="214" t="s">
+      <c r="T4" s="218" t="s">
         <v>83</v>
       </c>
-      <c r="U4" s="211"/>
-      <c r="V4" s="211"/>
-      <c r="W4" s="211"/>
-      <c r="X4" s="211"/>
-      <c r="Y4" s="212"/>
-      <c r="Z4" s="215" t="s">
+      <c r="U4" s="215"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="215"/>
+      <c r="X4" s="215"/>
+      <c r="Y4" s="216"/>
+      <c r="Z4" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="AA4" s="216" t="s">
+      <c r="AA4" s="210" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3583,7 +3589,7 @@
       <c r="B5" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="218">
+      <c r="C5" s="212">
         <v>27</v>
       </c>
       <c r="D5" s="204">
@@ -3651,13 +3657,13 @@
         <v>90</v>
       </c>
       <c r="Z5" s="202"/>
-      <c r="AA5" s="217"/>
+      <c r="AA5" s="211"/>
     </row>
     <row r="6" spans="2:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="219"/>
+      <c r="C6" s="213"/>
       <c r="D6" s="205"/>
       <c r="E6" s="205"/>
       <c r="F6" s="205"/>
@@ -3681,7 +3687,7 @@
       <c r="X6" s="202"/>
       <c r="Y6" s="197"/>
       <c r="Z6" s="202"/>
-      <c r="AA6" s="217"/>
+      <c r="AA6" s="211"/>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="82" t="s">
@@ -4205,7 +4211,7 @@
         <v>62</v>
       </c>
       <c r="V13" s="96" t="s">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="W13" s="79" t="s">
         <v>22</v>
@@ -5993,7 +5999,7 @@
     </row>
     <row r="37" spans="2:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="77" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="V37" s="79"/>
       <c r="Z37" s="79"/>
@@ -11288,12 +11294,12 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
